--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27360" windowHeight="15030"/>
   </bookViews>
   <sheets>
     <sheet name="copy" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <t>Woos</t>
   </si>
   <si>
-    <t>伍斯</t>
+    <t>吴氏</t>
   </si>
   <si>
     <t>spirit.hero.titleHighlight</t>
@@ -2107,7 +2107,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G141"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="36.8333333333333" customWidth="1"/>
     <col min="2" max="2" width="28.8333333333333" customWidth="1"/>
@@ -2323,8 +2323,6 @@
       <c r="C12" t="s">
         <v>9</v>
       </c>
-      <c r="D12"/>
-      <c r="E12"/>
       <c r="G12" t="s">
         <v>42</v>
       </c>

--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -398,15 +402,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G143"/>
-  <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="72.83203125" customWidth="1"/>
-    <col min="5" max="5" width="72.83203125" customWidth="1"/>
-    <col min="6" max="6" width="48.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -488,10 +483,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D4" t="str">
-        <v>Below: Season II episodes that are already filmed and published on the official playlist. This block is the episode index and viewing order for what has been shot.</v>
+        <v>Part of the video of the general outline of woos spirit medicine has been filmed as the content of the second season video</v>
       </c>
       <c r="E4" t="str">
-        <v>以下为官方播放列表中已发布、已拍摄的第二季视频目录；用于索引与收看顺序，与上方课程总纲衔接。</v>
+        <v>已拍摄灵魂医学总纲部分视频为第2季视频内容</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -511,10 +506,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D5" t="str">
-        <v>Hierarchical index aligned with the official Spirit Medicine page — tap a heading to jump to episodes below.</v>
+        <v>The following is a complete outline of the video file directory of woos spirit medicine. At present, only a small part of it has been filmed, and most of the content has not yet been completed.</v>
       </c>
       <c r="E5" t="str">
-        <v>与官网 Spirit Medicine 栏目结构一致的层级索引 — 点击标题可跳转至下方正片列表。</v>
+        <v>以下是完整的灵魂医学的视频档案目录大纲。目前只拍摄了其中的一小部分，绝大部分内容尚未完成。</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -546,7 +541,7 @@
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>spirit.hero.body</v>
       </c>
@@ -557,10 +552,13 @@
         <v>paragraph / other</v>
       </c>
       <c r="D7" t="str">
-        <v>This documentary scientifically reveals the Human Spirit (Soul) Medicine — organs, physiological systems, and basic pathology of the Spirit (Soul), along with the evidence and pathogenesis of Spirit (Ghost) harm to the human host after death.</v>
-      </c>
-      <c r="E7" t="str">
-        <v>本纪录片从科学角度揭示人类灵体体医学——灵的器官、生理系统与基本病理，以及亡后灵体对人体宿主造成伤害的证据与发病机制。</v>
+        <v>This documentary reveals spirit medicine from a scientific point of view-both before and after death. Before death: physiology and basic pathology of organs and physiological systems of human spirit soul. The video focuses on the evidence and pathogenesis of the harm caused by spirit ghost attachment to human hosts. After Death: Organ, Physiological System and Basic Pathology of spirits ghosts</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">本纪录片从科学角度揭示灵魂医学——包括生前和死后。
+生前：人类灵体的器官、生理系统等生理学和基本病理。
+视频重点是鬼魂附体对人类宿主造成伤害的证据与发病机制。
+死后：鬼魂的器官、生理系统与基本病理</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -583,7 +581,7 @@
         <v>Woos</v>
       </c>
       <c r="E8" t="str">
-        <v>伍斯</v>
+        <v>吴氏</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -606,7 +604,7 @@
         <v>Spirit Medicine</v>
       </c>
       <c r="E9" t="str">
-        <v>灵体医学</v>
+        <v>灵魂医学</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -698,7 +696,7 @@
         <v>Woos Spirit Medicine</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>吴氏灵魂医学</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -718,10 +716,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D14" t="str">
-        <v>Healing methodologies connecting the physical body and ethereal consciousness. This season focuses on practical intervention, structured recovery pathways, and ongoing restoration of balance for mind and soul.</v>
+        <v>Reveals spirit medicine from a scientific point of view-both before and after death.</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>从科学角度揭示灵魂医学——包括生前和死后</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -741,10 +739,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D15" t="str">
-        <v>Episode list follows the official YouTube playlist; FILE groups on /spirit-medicine are ordered 2-1, 2-2, 2-4, 2-3, 2-5. Use “Full curriculum outline” for the ess-esw.org-style directory.</v>
+        <v>This table of contents is in normal order, and the following link tables are arranged in the recommended viewing order.</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>该目录为正常顺序，下方链接表则按照推荐观看顺序排列</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -764,10 +762,10 @@
         <v>heading</v>
       </c>
       <c r="D16" t="str">
-        <v>Season II — Spirit Medicine (YouTube playlist)</v>
+        <v>Season II — Woos Spirit Medicine</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>第二季 ---- 吴氏灵魂医学</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -790,7 +788,7 @@
         <v>FILE 2-1</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>档案 2-1</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -813,7 +811,7 @@
         <v>File 2-1 Abstract of Spirit Medicine</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>档案 2-1 灵魂医学总介绍</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -836,7 +834,7 @@
         <v>Abstract &amp; scope of Spirit Medicine · 9 min</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>灵魂医学总纲与摘要 总时长 -- 9分钟</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -859,7 +857,7 @@
         <v>FILE 2-2</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>档案 2-2</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -882,7 +880,7 @@
         <v>FILE 2-2 Evidence of existence of spirits(ghosts)</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>档案 2-2 鬼魂存在的证据</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -905,7 +903,7 @@
         <v>Evidence for the existence of spirits (ghosts) · 13 min</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>鬼魂存在的证据 总时长 -- 13分钟</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -928,7 +926,7 @@
         <v>FILE 2-3-2-1-1</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>档案 2-3-2-1-1</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -951,7 +949,7 @@
         <v>File 2-3-2-1-1 Spiritual brain located in the flesh brain</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>档案 2-3-2-1-1  位于肉脑的灵脑器官</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -974,7 +972,7 @@
         <v>Human spirit (soul) physiology — spiritual brain &amp; memory · 36 min</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>人类灵魂生理学系列 ---灵脑器官  总时长 -- 36分钟</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -997,7 +995,7 @@
         <v>FILE 2-3-2-1-2</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>档案 2-3-2-1-2</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1020,7 +1018,7 @@
         <v>File 2-3-2-1-2 Spiritual-Brain Organs Located in the Heart</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>档案 2-3-2-1-2  位于心脏的灵脑器官</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1043,7 +1041,7 @@
         <v>Human spirit (soul) physiology — spiritual brain &amp; memory · 50 min</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>人类灵魂生理学系列 ---灵脑器官  总时长 -- 50分钟</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1066,7 +1064,7 @@
         <v>FILE 2-3-2-1-3</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>档案 2-3-2-1-3</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1089,7 +1087,7 @@
         <v>File 2-3-2-1-3 Spiritual-Brain Long-Term Memory Organ Located in the Cloud of the Ethereal Realm</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>档案 2-3-2-1-3  位于灵虚世界云端的灵脑记忆器官</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1112,7 +1110,7 @@
         <v>Human spirit (soul) physiology — spiritual brain &amp; memory · 18 min</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>人类灵魂生理学系列 ---灵脑器官  总时长 -- 18分钟</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -1135,7 +1133,7 @@
         <v>FILE 2-4-1-1</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>档案 2-4-1-1</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1158,7 +1156,7 @@
         <v>File 2-4-1-1 Overview,classification &amp; statistical data of America Spirit(ghost)</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>档案 2-4-1-1  美国鬼魂的概况，分类和统计学数据</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -1181,7 +1179,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 30 min</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--30分钟</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1204,7 +1202,7 @@
         <v>FILE 2-4-1-2</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>档案 2-4-1-2</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -1227,7 +1225,7 @@
         <v>File 2-4-1-2 The disposition of American spirit (Ghost) &amp; Possibility of Organized Harm to Humans</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>档案 2-4-1-2  美国鬼魂的秉性，有组织侵害人类的可能性</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -1250,7 +1248,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 27 min</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--27分钟</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -1273,7 +1271,7 @@
         <v>FILE 2-4-1-3</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>档案 2-4-1-3</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -1296,7 +1294,7 @@
         <v>File 2-4-1-3 The Physiological State of American spirit(ghost): Memory and Energy Metabolism</v>
       </c>
       <c r="E39" t="str">
-        <v/>
+        <v>档案 2-4-1-3  美国鬼魂的生理状况之记忆和能量</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -1319,7 +1317,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 29 min</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--29分钟</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -1342,7 +1340,7 @@
         <v>FILE 2-4-1-4</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>档案 2-4-1-4</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -1365,7 +1363,7 @@
         <v>File 2-4-1-4 The Physiological State of American spirit(ghost): Thinking and Emotion</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>档案 2-4-1-4  美国鬼魂的生理状况之思维和情绪</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -1388,7 +1386,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 36 min</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--36分钟</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -1411,7 +1409,7 @@
         <v>FILE 2-4-1-5-1</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>档案 2-4-1-5-1</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -1434,7 +1432,7 @@
         <v>File 2-4-1-5-1 The remote port organ (1)</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>档案 2-4-1-5-1 远程端口器官 （1）</v>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -1457,7 +1455,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 1h 13m</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--1小时 13分钟</v>
       </c>
       <c r="F46" t="str">
         <v/>
@@ -1480,7 +1478,7 @@
         <v>FILE 2-4-1-5-2</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>档案 2-4-1-5-2</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -1503,7 +1501,7 @@
         <v>File 2-4-1-5-2 The remote port organ (2)</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>档案 2-4-1-5-2 远程端口器官 （2）</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -1526,7 +1524,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 40 min</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--40分钟</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -1549,7 +1547,7 @@
         <v>FILE 2-4-1-6-1</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>档案 2-4-1-6-1</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -1572,7 +1570,7 @@
         <v>File 2-4-1-6-1 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (1)</v>
       </c>
       <c r="E51" t="str">
-        <v/>
+        <v>档案 2-4-1-6-1  医生和心理学家的抑郁症高发病率和原因（1）</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -1595,7 +1593,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 18 min</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--18分钟</v>
       </c>
       <c r="F52" t="str">
         <v/>
@@ -1618,7 +1616,7 @@
         <v>FILE 2-4-1-6-2</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>档案 2-4-1-6-2</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -1641,7 +1639,7 @@
         <v>File 2-4-1-6-2 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (2)</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>档案 2-4-1-6-2  医生和心理学家的抑郁症高发病率和原因（2）</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -1664,7 +1662,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles · 59 min</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>美国鬼魂：概览，生理及临床视角 总时长--59分钟</v>
       </c>
       <c r="F55" t="str">
         <v/>
@@ -1687,7 +1685,7 @@
         <v>FILE 2-5-2-1-1</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>档案 2-5-2-1-1</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -1710,7 +1708,7 @@
         <v>File 2-5-2-1-1 Pathological Principles of Schizophrenia and Dissociative Disorders (1)</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>档案 2-5-2-1-1  精神分裂症和分离性障碍的病理学原理（1）</v>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -1733,7 +1731,7 @@
         <v>Pathology of the human spirit &amp; possession effects on the host · 26 min</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>人类灵体病理学与附体病理学   总时长----26分钟</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -1756,7 +1754,7 @@
         <v>FILE 2-5-2-1-2</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>档案 2-5-2-1-2</v>
       </c>
       <c r="F59" t="str">
         <v/>
@@ -1779,7 +1777,7 @@
         <v>File 2-5-2-1-2 Pathological Principles of Schizophrenia and Dissociative Disorders (2)</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>档案 2-5-2-1-2  精神分裂症和分离性障碍的病理学原理（2）</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -1802,7 +1800,7 @@
         <v>Pathology of the human spirit &amp; possession effects on the host · 26 min</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>人类灵体病理学与附体病理学   总时长----26分钟</v>
       </c>
       <c r="F61" t="str">
         <v/>
@@ -1825,7 +1823,7 @@
         <v>FILE 2-5-2-2</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>档案 2-5-2-2</v>
       </c>
       <c r="F62" t="str">
         <v/>
@@ -1848,7 +1846,7 @@
         <v>File 2-5-2-2 The Comprehensive Impact of Possessing spirit ghost on the Human Host's flesh body</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>档案 2-5-2-2  附体鬼魂对人类宿主肉体带来的全方位影响</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -1871,7 +1869,7 @@
         <v>Pathology of the human spirit &amp; possession effects on the host · 34 min</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>人类灵体病理学与附体病理学   总时长----34分钟</v>
       </c>
       <c r="F64" t="str">
         <v/>
@@ -1894,7 +1892,7 @@
         <v>FILE 2-5-2-3</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>档案 2-5-2-3</v>
       </c>
       <c r="F65" t="str">
         <v/>
@@ -1917,7 +1915,7 @@
         <v>File 2-5-2-3 Soul Pathology Principles &amp; Healing Strategies for Various Emotional Disorders</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>档案 2-5-2-3  各类情绪障碍灵魂病理学原理以及疗愈对策</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -1940,7 +1938,7 @@
         <v>Pathology of the human spirit &amp; possession effects on the host · 30 min</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>人类灵体病理学与附体病理学   总时长----30分钟</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -1963,7 +1961,7 @@
         <v>FILE 2-1</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>档案 2-1</v>
       </c>
       <c r="F68" t="str">
         <v/>
@@ -1983,10 +1981,10 @@
         <v>heading</v>
       </c>
       <c r="D69" t="str">
-        <v>General Principles and Definition of Spirit Medicine</v>
+        <v>Abstract of Spirit Medicine</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>灵魂医学总介绍</v>
       </c>
       <c r="F69" t="str">
         <v/>
@@ -2009,7 +2007,7 @@
         <v>FILE 2-2</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>档案 2-2</v>
       </c>
       <c r="F70" t="str">
         <v/>
@@ -2029,10 +2027,10 @@
         <v>heading</v>
       </c>
       <c r="D71" t="str">
-        <v>Evidence for the Existence of Spirits (Ghosts)</v>
+        <v>Evidence of existence of spirits(ghosts)</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>鬼魂存在的证据</v>
       </c>
       <c r="F71" t="str">
         <v/>
@@ -2055,7 +2053,7 @@
         <v>FILE 2-3</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>档案 2-3</v>
       </c>
       <c r="F72" t="str">
         <v/>
@@ -2078,7 +2076,7 @@
         <v>Human Spirit (Soul) Physiology</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>人类灵魂生理学</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -2101,7 +2099,7 @@
         <v>2-3-1</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>2-3-1</v>
       </c>
       <c r="F74" t="str">
         <v/>
@@ -2124,7 +2122,7 @@
         <v>Understand the Spirit (Soul) from Meridians</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>从经络开始认知人类灵魂</v>
       </c>
       <c r="F75" t="str">
         <v/>
@@ -2147,7 +2145,7 @@
         <v>2-3-2</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>2-3-2</v>
       </c>
       <c r="F76" t="str">
         <v/>
@@ -2170,7 +2168,7 @@
         <v>Physiological Systems of Spirit (Soul)</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>人类灵魂生理系统</v>
       </c>
       <c r="F77" t="str">
         <v/>
@@ -2193,7 +2191,7 @@
         <v>FILE 2-4</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>档案 2-4</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -2216,7 +2214,7 @@
         <v>Overview: Physiology &amp; Pathology of Spirits (Ghosts)</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>概览：鬼魂生理，病理学</v>
       </c>
       <c r="F79" t="str">
         <v/>
@@ -2239,7 +2237,7 @@
         <v>2-4-1</v>
       </c>
       <c r="E80" t="str">
-        <v/>
+        <v>2-4-1</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -2259,10 +2257,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D81" t="str">
-        <v>Overview: American Spirits (Ghosts)</v>
+        <v>Overview,classification &amp; statistical data of America Spirit(ghost)</v>
       </c>
       <c r="E81" t="str">
-        <v/>
+        <v xml:space="preserve"> 美国鬼魂的概况，分类和统计学数据</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -2285,7 +2283,7 @@
         <v>2-4-2</v>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>2-4-2</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -2308,7 +2306,7 @@
         <v>PSI Ability of Spirits (Ghosts)</v>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>鬼魂的超自然能力</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -2331,7 +2329,7 @@
         <v>2-4-3</v>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>2-4-3</v>
       </c>
       <c r="F84" t="str">
         <v/>
@@ -2354,7 +2352,7 @@
         <v>Process of Human Death &amp; the Birth of a Ghost</v>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>人类的死亡以及鬼魂的诞生过程</v>
       </c>
       <c r="F85" t="str">
         <v/>
@@ -2400,7 +2398,7 @@
         <v>The Intersection of Spirits (Ghosts) &amp; the Physical World</v>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>鬼魂与现实世界的交互</v>
       </c>
       <c r="F87" t="str">
         <v/>
@@ -2446,7 +2444,7 @@
         <v>Mutual Harm &amp; Death Among Spirits (Ghosts)</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>鬼魂之间的互相伤害以及死亡现象</v>
       </c>
       <c r="F89" t="str">
         <v/>
@@ -2492,7 +2490,7 @@
         <v>Basic Pathology of Spirits (Ghosts)</v>
       </c>
       <c r="E91" t="str">
-        <v/>
+        <v>基础鬼魂病理学</v>
       </c>
       <c r="F91" t="str">
         <v/>
@@ -2515,7 +2513,7 @@
         <v>FILE 2-5</v>
       </c>
       <c r="E92" t="str">
-        <v/>
+        <v>档案 2-5</v>
       </c>
       <c r="F92" t="str">
         <v/>
@@ -2538,7 +2536,7 @@
         <v>Pathology of Human Spirit (Soul)</v>
       </c>
       <c r="E93" t="str">
-        <v/>
+        <v>人类灵魂病理学</v>
       </c>
       <c r="F93" t="str">
         <v/>
@@ -2584,7 +2582,7 @@
         <v>Intrinsic Pathology of the Human Spirit (Soul) Body</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>人类自体灵魂的病理学</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -2630,7 +2628,7 @@
         <v>Diseases Caused by Possessed Spirits (Ghosts)</v>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>附体鬼魂带来的疾病</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -2676,7 +2674,7 @@
         <v>Harmonious Coexistence of Humans and Spirits (Ghosts)</v>
       </c>
       <c r="E99" t="str">
-        <v/>
+        <v>人类与鬼魂的和谐共生</v>
       </c>
       <c r="F99" t="str">
         <v/>
@@ -2699,7 +2697,7 @@
         <v>FILE 2-1</v>
       </c>
       <c r="E100" t="str">
-        <v/>
+        <v>档案 2-1</v>
       </c>
       <c r="F100" t="str">
         <v/>
@@ -2719,10 +2717,10 @@
         <v>heading</v>
       </c>
       <c r="D101" t="str">
-        <v>Abstract &amp; scope of Spirit Medicine</v>
+        <v>Abstract of Spirit Medicine</v>
       </c>
       <c r="E101" t="str">
-        <v/>
+        <v>灵魂医学总介绍</v>
       </c>
       <c r="F101" t="str">
         <v/>
@@ -2768,7 +2766,7 @@
         <v>File 2-1 Abstract of Spirit Medicine</v>
       </c>
       <c r="E103" t="str">
-        <v/>
+        <v>档案 2-1  灵魂医学总介绍</v>
       </c>
       <c r="F103" t="str">
         <v/>
@@ -2791,7 +2789,7 @@
         <v>FILE 2-2</v>
       </c>
       <c r="E104" t="str">
-        <v/>
+        <v>档案 2-2</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -2811,10 +2809,10 @@
         <v>heading</v>
       </c>
       <c r="D105" t="str">
-        <v>Evidence for the existence of spirits (ghosts)</v>
+        <v>Evidence of existence of spirits(ghosts)</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>鬼魂存在的证据</v>
       </c>
       <c r="F105" t="str">
         <v/>
@@ -2860,7 +2858,7 @@
         <v>FILE 2-2 Evidence of existence of spirits(ghosts)</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>档案 2-2  鬼魂存在的证据</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -2883,7 +2881,7 @@
         <v>FILE 2-3</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>档案 2-3</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -2903,10 +2901,10 @@
         <v>heading</v>
       </c>
       <c r="D109" t="str">
-        <v>Human spirit (soul) physiology — spiritual brain &amp; memory</v>
+        <v>Human spirit (soul) physiology — spiritual brain organ</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>人类灵魂生理学 ----灵脑器官</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -2952,7 +2950,7 @@
         <v>File 2-3-2-1-1 Spiritual brain located in the flesh brain</v>
       </c>
       <c r="E111" t="str">
-        <v/>
+        <v>档案 2-3-2-1-1  位于肉脑的灵脑器官</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -2998,7 +2996,7 @@
         <v>File 2-3-2-1-2 Spiritual-Brain Organs Located in the Heart</v>
       </c>
       <c r="E113" t="str">
-        <v/>
+        <v>档案 2-3-2-1-2  位于心脏的灵脑器官</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -3044,7 +3042,7 @@
         <v>File 2-3-2-1-3 Spiritual-Brain Long-Term Memory Organ Located in the Cloud of the Ethereal Realm</v>
       </c>
       <c r="E115" t="str">
-        <v/>
+        <v>档案 2-3-2-1-3  位于灵虚世界云端的灵脑记忆器官</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -3067,7 +3065,7 @@
         <v>FILE 2-4</v>
       </c>
       <c r="E116" t="str">
-        <v/>
+        <v>档案 2-4</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -3090,7 +3088,7 @@
         <v>American spirit (ghost): overview, physiology &amp; clinical angles</v>
       </c>
       <c r="E117" t="str">
-        <v/>
+        <v xml:space="preserve">美国鬼魂：概览，生理及临床视角 </v>
       </c>
       <c r="F117" t="str">
         <v/>
@@ -3136,7 +3134,7 @@
         <v>File 2-4-1-1 Overview,classification &amp; statistical data of America Spirit(ghost)</v>
       </c>
       <c r="E119" t="str">
-        <v/>
+        <v>档案 2-4-1-1  美国鬼魂的概况，分类和统计学数据</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -3182,7 +3180,7 @@
         <v>File 2-4-1-2 The disposition of American spirit (Ghost) &amp; Possibility of Organized Harm to Humans</v>
       </c>
       <c r="E121" t="str">
-        <v/>
+        <v>档案 2-4-1-2  美国鬼魂的秉性，有组织侵害人类的可能性</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -3228,7 +3226,7 @@
         <v>File 2-4-1-3 The Physiological State of American spirit(ghost): Memory and Energy Metabolism</v>
       </c>
       <c r="E123" t="str">
-        <v/>
+        <v>档案 2-4-1-3  美国鬼魂的生理状况之记忆和能量</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -3274,7 +3272,7 @@
         <v>File 2-4-1-4 The Physiological State of American spirit(ghost): Thinking and Emotion</v>
       </c>
       <c r="E125" t="str">
-        <v/>
+        <v>档案 2-4-1-4  美国鬼魂的生理状况之思维和情绪</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -3320,7 +3318,7 @@
         <v>File 2-4-1-5-1 The remote port organ (1)</v>
       </c>
       <c r="E127" t="str">
-        <v/>
+        <v>档案 2-4-1-5-1 远程端口器官 （1）</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -3366,7 +3364,7 @@
         <v>File 2-4-1-5-2 The remote port organ (2)</v>
       </c>
       <c r="E129" t="str">
-        <v/>
+        <v>档案 2-4-1-5-2  远程端口器官 （2）</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -3412,7 +3410,7 @@
         <v>File 2-4-1-6-1 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (1)</v>
       </c>
       <c r="E131" t="str">
-        <v/>
+        <v>档案 2-4-1-6-1  医生和心理学家的抑郁症高发病率和原因（1）</v>
       </c>
       <c r="F131" t="str">
         <v/>
@@ -3458,7 +3456,7 @@
         <v>File 2-4-1-6-2 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (2)</v>
       </c>
       <c r="E133" t="str">
-        <v/>
+        <v>档案 2-4-1-6-2  医生和心理学家的抑郁症高发病率和原因（2）</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -3481,7 +3479,7 @@
         <v>FILE 2-5</v>
       </c>
       <c r="E134" t="str">
-        <v/>
+        <v>档案 2-5</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -3504,7 +3502,7 @@
         <v>Pathology of the human spirit &amp; possession effects on the host</v>
       </c>
       <c r="E135" t="str">
-        <v/>
+        <v>人类灵体病理学与附体病理学</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -3550,7 +3548,7 @@
         <v>File 2-5-2-1-1 Pathological Principles of Schizophrenia and Dissociative Disorders (1)</v>
       </c>
       <c r="E137" t="str">
-        <v/>
+        <v>档案 2-5-2-1-1  精神分裂症和分离性障碍的病理学原理（1）</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -3596,7 +3594,7 @@
         <v>File 2-5-2-1-2 Pathological Principles of Schizophrenia and Dissociative Disorders (2)</v>
       </c>
       <c r="E139" t="str">
-        <v/>
+        <v>档案 2-5-2-1-2  精神分裂症和分离性障碍的病理学原理（2）</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -3642,7 +3640,7 @@
         <v>File 2-5-2-2 The Comprehensive Impact of Possessing spirit ghost on the Human Host's flesh body</v>
       </c>
       <c r="E141" t="str">
-        <v/>
+        <v>档案 2-5-2-2  附体鬼魂对人类宿主肉体带来的全方位影响</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -3688,7 +3686,7 @@
         <v>File 2-5-2-3 Soul Pathology Principles &amp; Healing Strategies for Various Emotional Disorders</v>
       </c>
       <c r="E143" t="str">
-        <v/>
+        <v>档案 2-5-2-3  各类情绪障碍灵魂病理学原理以及疗愈对策</v>
       </c>
       <c r="F143" t="str">
         <v/>

--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -483,7 +483,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D4" t="str">
-        <v>Part of the video of the general outline of woos spirit medicine has been filmed as the content of the second season video</v>
+        <v>Part of the general outline of **Woos Spirit Medicine** has been filmed as the second-season video content.</v>
       </c>
       <c r="E4" t="str">
         <v>已拍摄灵魂医学总纲部分视频，为第 2 季视频内容</v>
@@ -506,7 +506,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D5" t="str">
-        <v>The following is a complete outline of the video file directory of woos spirit medicine. At present, only a small part of it has been filmed, and most of the content has not yet been completed.</v>
+        <v>The following is the complete video directory outline for **Woos Spirit Medicine**. Only a small part has been filmed; most content is not yet complete.</v>
       </c>
       <c r="E5" t="str">
         <v>以下是完整的灵魂医学的视频档案目录大纲。目前只拍摄了其中的一小部分，绝大部分内容尚未完成。</v>
@@ -552,7 +552,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D7" t="str">
-        <v>This documentary reveals spirit medicine from a scientific point of view-both before and after death. Before death: physiology and basic pathology of organs and physiological systems of human spirit soul. The video focuses on the evidence and pathogenesis of the harm caused by spirit ghost attachment to human hosts. After Death: Organ, Physiological System and Basic Pathology of spirits ghosts</v>
+        <v>**Woos Spirit Medicine** is a documentary series on spirit healing from a scientific perspective—before and after death. Before death: physiology and basic pathology of organs and systems of the human **spirit (soul)**. Focus: evidence and pathogenesis of harm from **spirit (ghost)** attachment to hosts. After death: organs, physiological systems, and basic pathology of **spirits (ghosts)**.</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
         <v xml:space="preserve">本纪录片从科学角度揭示灵魂医学——包括生前和死后。
@@ -716,7 +716,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D14" t="str">
-        <v>Reveals spirit medicine from a scientific point of view-both before and after death.</v>
+        <v>**Woos Spirit Medicine** reveals spirit healing from a scientific perspective—both before and after death.</v>
       </c>
       <c r="E14" t="str">
         <v>从科学角度揭示灵魂医学——包括生前和死后</v>
@@ -1728,7 +1728,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D58" t="str">
-        <v>Pathology of the human spirit &amp; possession effects on the host · 26 min</v>
+        <v>Pathology of the human **spirit** &amp; possession effects on the host · 26 min</v>
       </c>
       <c r="E58" t="str">
         <v>人类灵体病理学与附体病理学   总时长----26分钟</v>
@@ -1797,7 +1797,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D61" t="str">
-        <v>Pathology of the human spirit &amp; possession effects on the host · 26 min</v>
+        <v>Pathology of the human **spirit** &amp; possession effects on the host · 26 min</v>
       </c>
       <c r="E61" t="str">
         <v>人类灵体病理学与附体病理学   总时长----26分钟</v>
@@ -1866,7 +1866,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D64" t="str">
-        <v>Pathology of the human spirit &amp; possession effects on the host · 34 min</v>
+        <v>Pathology of the human **spirit** &amp; possession effects on the host · 34 min</v>
       </c>
       <c r="E64" t="str">
         <v>人类灵体病理学与附体病理学   总时长----34分钟</v>
@@ -1935,7 +1935,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D67" t="str">
-        <v>Pathology of the human spirit &amp; possession effects on the host · 30 min</v>
+        <v>Pathology of the human **spirit** &amp; possession effects on the host · 30 min</v>
       </c>
       <c r="E67" t="str">
         <v>人类灵体病理学与附体病理学   总时长----30分钟</v>

--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -2878,10 +2878,10 @@
         <v>label</v>
       </c>
       <c r="D108" t="str">
-        <v>FILE 2-3</v>
+        <v>FILE 2-3-2-1</v>
       </c>
       <c r="E108" t="str">
-        <v>档案 2-3</v>
+        <v>档案 2-3-2-1</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -2993,7 +2993,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D113" t="str">
-        <v>File 2-3-2-1-2 Spiritual-Brain Organs Located in the Heart</v>
+        <v>File 2-3-2-1-2 Spiritual Brain Located in the Heart</v>
       </c>
       <c r="E113" t="str">
         <v>位于心脏的灵脑器官</v>
@@ -3039,7 +3039,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D115" t="str">
-        <v>File 2-3-2-1-3 Spiritual-Brain Long-Term Memory Organ Located in the Cloud of the Ethereal Realm</v>
+        <v>File 2-3-2-1-3 Spiritual Brain Long-Term Memory Organ Located in the Cloud of the Ethereal Realm</v>
       </c>
       <c r="E115" t="str">
         <v>位于灵虚世界云端的灵脑记忆器官</v>
@@ -3062,10 +3062,10 @@
         <v>label</v>
       </c>
       <c r="D116" t="str">
-        <v>FILE 2-4</v>
+        <v>FILE 2-4-1</v>
       </c>
       <c r="E116" t="str">
-        <v>档案 2-4</v>
+        <v>档案 2-4-1</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -3476,10 +3476,10 @@
         <v>label</v>
       </c>
       <c r="D134" t="str">
-        <v>FILE 2-5</v>
+        <v>FILE 2-5-2</v>
       </c>
       <c r="E134" t="str">
-        <v>档案 2-5</v>
+        <v>档案 2-5-2</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -3499,10 +3499,10 @@
         <v>heading</v>
       </c>
       <c r="D135" t="str">
-        <v>Pathology of the human spirit &amp; possession effects on the host</v>
+        <v>Diseases caused by possessed spirits(ghosts)</v>
       </c>
       <c r="E135" t="str">
-        <v>人类灵体病理学与附体病理学</v>
+        <v>附体灵体导致的疾病</v>
       </c>
       <c r="F135" t="str">
         <v/>
